--- a/disease_registry/outputs/Banana/internet.xlsx
+++ b/disease_registry/outputs/Banana/internet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yellow_And_Black_Sigatoka</t>
+          <t>Panama_Disease</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mycosphaerella fijiensis</t>
+          <t>Fusarium oxysporum f. sp. cubense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,12 +471,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Foliar</t>
+          <t>Root, Vascular, Foliar, Stem, Whole plant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Black streaks and spots on leaves that cause reduced photosynthesis and defoliation, severely reducing banana bunch yield and fruit quality.. Black streaks and spots that lack the distinct yellow halo characteristic of Yellow Sigatoka.. Yellow Sigatoka</t>
+          <t>Vascular wilt disease causing internal vascular discolouration ranging from pale yellow to dark red or black, external wilting and yellowing of older leaves, leaf collapse at the petiole, and splitting of the pseudostem base, eventually killing the plant.. Characteristic internal vascular discolouration varying from pale yellow in early stages to dark red or almost black in later stages. Yellowing and wilting progresses from older to younger leaves. Collapsed leaves hang down the pseudostem like a skirt. Splitting of the base of the pseudostem. Vascular discoloration is peripheral in the pseudostem (not concentrated near center). Fruit does not show any specific disease symptoms. Does not cause wilting and blackening of young suckers or dry rot in fruit.. Moko disease, Xanthomonas wilt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,23 +491,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cigar_End_Rot</t>
+          <t>Yellow_And_Black_Sigatoka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verticillium theobromae</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Mycosphaerella fijiensis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fruit, Peduncle, Pulp</t>
+          <t>Foliar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The infection causes blackening of fruit skin with shrinkage and folding of tissues, which become corrugated and covered with powdery grey conidia resembling ash. Dry rot develops in the pulp, making affected tissues dry and fibrous.. Corrugated tissues covered with powdery grey conidia resembling ash on a cigar end</t>
+          <t>Black streaks and spots on leaves leading to reduced photosynthesis and defoliation, reducing bunch yield and fruit quality.. Early streaks and spots are black and lack the distinct yellow halo present in young streaks of Yellow Sigatoka. The first symptom is chlorotic flecking appearing about 15-20 days after infection, with lesions forming on the undersurface of the leaf.. Yellow Sigatoka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -522,42 +526,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cordana_Leaf_Spot</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Neocordana musae and Neocordana johnstonii</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Foliar</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Large, pale brown, oval to fusiform necrotic lesions with pale grey concentric ring patterns and dark brown borders surrounded by bright yellow halos. Lesions coalesce into large necrotic patches, and leaves ultimately turn brown and dry out.. Pale grey concentric ring patterns with dark brown border surrounded by bright yellow halo. Spots caused by N. musae are larger and oval to elliptical, while N. johnstonii spots are smaller and become more fusiform with age. Spores produced in large quantities on the underside of leaves, appearing as greyish-brown and hairy.</t>
-        </is>
-      </c>
+          <t>Anthracnose</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anthracnose</t>
+          <t>Banana_Bunchy_Top_Virus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -576,7 +564,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Banana_Bunchy_Top_Virus</t>
+          <t>Bunchy_Top</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -595,7 +583,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bunchy_Top</t>
+          <t>Cigar_End_Rot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -614,7 +602,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Panama_Disease</t>
+          <t>Cordana_Leaf_Spot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
